--- a/artfynd/A 2921-2021 artfynd.xlsx
+++ b/artfynd/A 2921-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2921-2021 artfynd.xlsx
+++ b/artfynd/A 2921-2021 artfynd.xlsx
@@ -819,12 +819,7 @@
         <v>63225741</v>
       </c>
       <c r="B3" t="n">
-        <v>57508</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,10 +875,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558697.0689867269</v>
+        <v>558697</v>
       </c>
       <c r="R3" t="n">
-        <v>6250529.245165119</v>
+        <v>6250529</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,19 +908,9 @@
           <t>2011-06-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-06-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 2921-2021 artfynd.xlsx
+++ b/artfynd/A 2921-2021 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>63225741</v>
       </c>
       <c r="B3" t="n">
-        <v>56613</v>
+        <v>56615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2921-2021 artfynd.xlsx
+++ b/artfynd/A 2921-2021 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>63225741</v>
       </c>
       <c r="B3" t="n">
-        <v>56615</v>
+        <v>56617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2921-2021 artfynd.xlsx
+++ b/artfynd/A 2921-2021 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>63225741</v>
       </c>
       <c r="B3" t="n">
-        <v>56617</v>
+        <v>56620</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
